--- a/web/storage/app/templates/timesheet_template.xlsx
+++ b/web/storage/app/templates/timesheet_template.xlsx
@@ -15,18 +15,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4">
-  <si>
-    <t>Consultant</t>
-  </si>
-  <si>
-    <t>Pay Period Start</t>
-  </si>
-  <si>
-    <t>Pay Period End</t>
-  </si>
-  <si>
-    <t>Total Hours</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+  <si>
+    <t>BI-WEEKLY TIMESHEET</t>
+  </si>
+  <si>
+    <t>Consultant:</t>
+  </si>
+  <si>
+    <t>Pay Period Start:</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>Pay Period End:</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>DAY</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>HOURS</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>Tue</t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>Fri</t>
+  </si>
+  <si>
+    <t>Sat</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>TOTAL HOURS:</t>
   </si>
 </sst>
 </file>
@@ -34,7 +76,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -44,16 +86,40 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,12 +127,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,21 +451,177 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="true" style="0"/>
+    <col min="2" max="2" width="10" customWidth="true" style="0"/>
+    <col min="3" max="3" width="30" customWidth="true" style="0"/>
+    <col min="7" max="7" width="12" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F6" s="3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="F25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="1">
+        <f>SUM(G10:G23)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/web/storage/app/templates/timesheet_template.xlsx
+++ b/web/storage/app/templates/timesheet_template.xlsx
@@ -26,13 +26,13 @@
     <t>Pay Period Start:</t>
   </si>
   <si>
-    <t>2026-03-24</t>
+    <t>2026-03-23</t>
   </si>
   <si>
     <t>Pay Period End:</t>
   </si>
   <si>
-    <t>2026-04-06</t>
+    <t>2026-04-05</t>
   </si>
   <si>
     <t>DATE</t>
@@ -75,7 +75,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;/&quot;mm&quot;/&quot;dd;@"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <b val="0"/>
@@ -146,12 +148,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,6 +507,9 @@
       </c>
     </row>
     <row r="10" spans="1:7">
+      <c r="A10" s="5">
+        <v>46104.0</v>
+      </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
@@ -512,6 +518,9 @@
       </c>
     </row>
     <row r="11" spans="1:7">
+      <c r="A11" s="5">
+        <v>46105.0</v>
+      </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
@@ -520,6 +529,9 @@
       </c>
     </row>
     <row r="12" spans="1:7">
+      <c r="A12" s="5">
+        <v>46106.0</v>
+      </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -528,6 +540,9 @@
       </c>
     </row>
     <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>46107.0</v>
+      </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -536,6 +551,9 @@
       </c>
     </row>
     <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>46108.0</v>
+      </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -544,6 +562,9 @@
       </c>
     </row>
     <row r="15" spans="1:7">
+      <c r="A15" s="5">
+        <v>46109.0</v>
+      </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
@@ -552,6 +573,9 @@
       </c>
     </row>
     <row r="16" spans="1:7">
+      <c r="A16" s="5">
+        <v>46110.0</v>
+      </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -560,6 +584,9 @@
       </c>
     </row>
     <row r="17" spans="1:7">
+      <c r="A17" s="5">
+        <v>46111.0</v>
+      </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
@@ -568,6 +595,9 @@
       </c>
     </row>
     <row r="18" spans="1:7">
+      <c r="A18" s="5">
+        <v>46112.0</v>
+      </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
@@ -576,6 +606,9 @@
       </c>
     </row>
     <row r="19" spans="1:7">
+      <c r="A19" s="5">
+        <v>46113.0</v>
+      </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
@@ -584,6 +617,9 @@
       </c>
     </row>
     <row r="20" spans="1:7">
+      <c r="A20" s="5">
+        <v>46114.0</v>
+      </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
@@ -592,6 +628,9 @@
       </c>
     </row>
     <row r="21" spans="1:7">
+      <c r="A21" s="5">
+        <v>46115.0</v>
+      </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
@@ -600,6 +639,9 @@
       </c>
     </row>
     <row r="22" spans="1:7">
+      <c r="A22" s="5">
+        <v>46116.0</v>
+      </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
@@ -608,6 +650,9 @@
       </c>
     </row>
     <row r="23" spans="1:7">
+      <c r="A23" s="5">
+        <v>46117.0</v>
+      </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
